--- a/results/thesis_tables.xlsx
+++ b/results/thesis_tables.xlsx
@@ -83,7 +83,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
@@ -5069,6 +5069,12 @@
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8.83203125" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
@@ -5077,7 +5083,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Baseline characteristic</t>
@@ -5131,7 +5137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve"> Single</t>

--- a/results/thesis_tables.xlsx
+++ b/results/thesis_tables.xlsx
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Hypothesis Testing (H1 &amp; H2)</t>
+          <t>Hypothesis Testing (H1)</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>Note. Master multi-pillar hypothesis evaluation matrix across Robustness, Resilience, and Generalizability. Demonstrates asymmetric trade-offs (H1) and confirms the values versus volatility paradigm (H2).</t>
+          <t>Note. Master multi-pillar hypothesis evaluation matrix across Robustness, Resilience, and Generalizability. Demonstrates asymmetric trade-offs (H1) and confirms the values versus volatility operational coupling.</t>
         </is>
       </c>
     </row>

--- a/results/thesis_tables.xlsx
+++ b/results/thesis_tables.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,6 +233,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1547,7 +1550,7 @@
       <c r="I6" s="26" t="n">
         <v>192160</v>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="31" t="inlineStr">
         <is>
           <t>+16.9%</t>
         </is>
@@ -1591,7 +1594,7 @@
       <c r="I7" s="26" t="n">
         <v>2738</v>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>+32.3%</t>
         </is>
@@ -1613,17 +1616,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>1.63%</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>1.47%</t>
         </is>
@@ -1638,12 +1641,12 @@
           <t>2.46% (LGA)</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>+14.1%</t>
         </is>
@@ -1687,7 +1690,7 @@
       <c r="I9" s="29" t="n">
         <v>14.21</v>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="31" t="inlineStr">
         <is>
           <t>+7.2%</t>
         </is>
@@ -1709,17 +1712,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>21.42%</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>3.30%</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>20.14%</t>
         </is>
@@ -1734,12 +1737,12 @@
           <t>28.07% (DFW)</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>20.31%</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="J10" s="31" t="inlineStr">
         <is>
           <t>+5.5%</t>
         </is>
@@ -1783,7 +1786,7 @@
       <c r="I11" s="29" t="n">
         <v>19.69</v>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J11" s="31" t="inlineStr">
         <is>
           <t>+4.5%</t>
         </is>
@@ -1827,7 +1830,7 @@
       <c r="I12" s="26" t="n">
         <v>68495531</v>
       </c>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J12" s="31" t="inlineStr">
         <is>
           <t>+3.9%</t>
         </is>
@@ -1871,7 +1874,7 @@
       <c r="I13" s="26" t="n">
         <v>51138</v>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="J13" s="31" t="inlineStr">
         <is>
           <t>+3.8%</t>
         </is>
@@ -1915,7 +1918,7 @@
       <c r="I14" s="29" t="n">
         <v>540.34</v>
       </c>
-      <c r="J14" s="30" t="inlineStr">
+      <c r="J14" s="31" t="inlineStr">
         <is>
           <t>-22.5%</t>
         </is>
@@ -1959,7 +1962,7 @@
       <c r="I15" s="26" t="n">
         <v>2784</v>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>-4.0%</t>
         </is>
@@ -1981,13 +1984,13 @@
           <t>ratio</t>
         </is>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <v>0.8728</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.2</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="36" t="n">
         <v>0.9064</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -2000,10 +2003,10 @@
           <t>1.1240 (LGA)</t>
         </is>
       </c>
-      <c r="I16" s="35" t="n">
+      <c r="I16" s="36" t="n">
         <v>0.825</v>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="J16" s="31" t="inlineStr">
         <is>
           <t>+5.8%</t>
         </is>
@@ -2025,17 +2028,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>47.45%</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>10.98%</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="31" t="inlineStr">
         <is>
           <t>44.41%</t>
         </is>
@@ -2050,12 +2053,12 @@
           <t>66.32% (DFW)</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t>51.39%</t>
         </is>
       </c>
-      <c r="J17" s="30" t="inlineStr">
+      <c r="J17" s="31" t="inlineStr">
         <is>
           <t>-7.7%</t>
         </is>
@@ -2077,17 +2080,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>52.55%</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>10.98%</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>55.59%</t>
         </is>
@@ -2102,12 +2105,12 @@
           <t>66.42% (EWR)</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>48.61%</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="31" t="inlineStr">
         <is>
           <t>+8.1%</t>
         </is>
@@ -2151,7 +2154,7 @@
       <c r="I19" s="26" t="n">
         <v>13103484</v>
       </c>
-      <c r="J19" s="30" t="inlineStr">
+      <c r="J19" s="31" t="inlineStr">
         <is>
           <t>+25.0%</t>
         </is>
@@ -2195,7 +2198,7 @@
       <c r="I20" s="29" t="n">
         <v>171.1</v>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="J20" s="31" t="inlineStr">
         <is>
           <t>-1.6%</t>
         </is>
@@ -2217,17 +2220,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>85.08%</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>0.82%</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>85.26%</t>
         </is>
@@ -2242,12 +2245,12 @@
           <t>86.12% (EWR)</t>
         </is>
       </c>
-      <c r="I21" s="31" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
         <is>
           <t>84.73%</t>
         </is>
       </c>
-      <c r="J21" s="31" t="inlineStr">
+      <c r="J21" s="32" t="inlineStr">
         <is>
           <t>+0.4%</t>
         </is>
@@ -2780,7 +2783,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="K14" s="34" t="n">
+      <c r="K14" s="35" t="n">
         <v>1.23</v>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -2875,10 +2878,10 @@
           <t>Lag t-1 (1 hr post-departure)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>0.1987</v>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>3.95%</t>
         </is>
@@ -2898,10 +2901,10 @@
           <t>Same-Hour Departure t (Gate departure)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>0.3403</v>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>11.58%</t>
         </is>
@@ -2921,10 +2924,10 @@
           <t>Lead t+1 (1 hr pre-departure)</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>0.4913</v>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>24.13%</t>
         </is>
@@ -2944,10 +2947,10 @@
           <t>Lead t+2 (2 hr pre-departure)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="36" t="n">
         <v>0.4876</v>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>23.78%</t>
         </is>
@@ -2967,10 +2970,10 @@
           <t>Lead t+3 (3 hr pre-departure)</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="36" t="n">
         <v>0.38</v>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>14.44%</t>
         </is>
@@ -2990,10 +2993,10 @@
           <t>Convolved Passenger Show-Up Curve</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>0.6985</v>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>48.78%</t>
         </is>
@@ -3013,15 +3016,15 @@
           <t>Show-Up Curve x T-100 Load Factor</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>0.7060999999999999</v>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>49.85%</t>
         </is>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <v>90.56</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -3156,22 +3159,22 @@
           <t>Daily Persistence Benchmark (y_t-24)</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="36" t="n">
         <v>0.4412</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="36" t="n">
         <v>0.6719000000000001</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="38" t="n">
         <v>253.6</v>
       </c>
-      <c r="G6" s="37" t="n">
+      <c r="G6" s="38" t="n">
         <v>179.3</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="37" t="n">
+      <c r="I6" s="38" t="n">
         <v>-0.7</v>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -3196,22 +3199,22 @@
           <t>Deterministic Flight Schedule Model (convolved show-up curve)</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>0.4912</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="36" t="n">
         <v>0.498</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="38" t="n">
         <v>313.4</v>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="38" t="n">
         <v>215.9</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="33" t="n">
         <v>0.945</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="38" t="n">
         <v>-42.1</v>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -3236,22 +3239,22 @@
           <t>Supervised Machine Learning Model (Decision Trees &amp; OTP)</t>
         </is>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="36" t="n">
         <v>0.5455</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>0.6178</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="38" t="n">
         <v>273.5</v>
       </c>
-      <c r="G8" s="37" t="n">
+      <c r="G8" s="38" t="n">
         <v>178</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="33" t="n">
         <v>0.779</v>
       </c>
-      <c r="I8" s="37" t="n">
+      <c r="I8" s="38" t="n">
         <v>-18.4</v>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -3276,22 +3279,22 @@
           <t>Dynamic Two-Stage Hybrid Model (Schedule + Real-time feedback)</t>
         </is>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="37" t="n">
         <v>0.712</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="37" t="n">
         <v>0.7483</v>
       </c>
-      <c r="F9" s="38" t="n">
+      <c r="F9" s="39" t="n">
         <v>222.1</v>
       </c>
-      <c r="G9" s="38" t="n">
+      <c r="G9" s="39" t="n">
         <v>142.8</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="34" t="n">
         <v>0.662</v>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="39" t="n">
         <v>-8.5</v>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -3472,10 +3475,10 @@
           <t>MASE &lt; 0.700</t>
         </is>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.945</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -3483,7 +3486,7 @@
           <t>0.680--0.700</t>
         </is>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="H7" s="33" t="n">
         <v>0.662</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -3607,13 +3610,13 @@
           <t>Lowest Shock MASE</t>
         </is>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="33" t="n">
         <v>1.082</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="33" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -3832,7 +3835,7 @@
           <t>Minimal Penalty (&lt;= 10%)</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -3879,7 +3882,7 @@
           <t>DeltaMASE &lt;= 10.0%</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -4019,10 +4022,10 @@
           <t>Daily Persistence Benchmark (y_t-24)</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="38" t="n">
         <v>253.6</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -4057,10 +4060,10 @@
           <t>Deterministic Flight Schedule Model</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="38" t="n">
         <v>313.4</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="33" t="n">
         <v>0.945</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -4095,7 +4098,7 @@
           <t>Supervised Machine Learning Model</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="38" t="n">
         <v>273.5</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -4135,10 +4138,10 @@
           <t>Dynamic Two-Stage Hybrid Model</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="39" t="n">
         <v>222.1</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="34" t="n">
         <v>0.662</v>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -4277,10 +4280,10 @@
           <t>Daily Persistence Benchmark (y_t-24)</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="38" t="n">
         <v>398.2</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="29" t="n">
@@ -4318,10 +4321,10 @@
           <t>Deterministic Flight Schedule Model</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="38" t="n">
         <v>412.8</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="33" t="n">
         <v>1.082</v>
       </c>
       <c r="F7" s="29" t="n">
@@ -4359,10 +4362,10 @@
           <t>Supervised Machine Learning Model</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="38" t="n">
         <v>318.4</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="33" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="F8" s="29" t="n">
@@ -4400,13 +4403,13 @@
           <t>Dynamic Two-Stage Hybrid Model</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="39" t="n">
         <v>254.2</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="34" t="n">
         <v>0.694</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>1.05</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -4545,21 +4548,21 @@
           <t>Daily Persistence Benchmark (y_t-24)</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="38" t="n">
         <v>253.6</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="38" t="n">
         <v>253.6</v>
       </c>
       <c r="F6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -4586,16 +4589,16 @@
           <t>Deterministic Flight Schedule Model</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="38" t="n">
         <v>313.4</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="38" t="n">
         <v>326.5</v>
       </c>
       <c r="F7" s="29" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>+4.2%</t>
         </is>
@@ -4627,16 +4630,16 @@
           <t>Supervised Machine Learning Model</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="38" t="n">
         <v>273.5</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="38" t="n">
         <v>295.1</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>1.08</v>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>+7.9%</t>
         </is>
@@ -4668,16 +4671,16 @@
           <t>Dynamic Two-Stage Hybrid Model</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="39" t="n">
         <v>222.1</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="39" t="n">
         <v>264.3</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <v>1.19</v>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>+19.0%</t>
         </is>
@@ -5581,18 +5584,14 @@
       <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>5,336.00</t>
-        </is>
+      <c r="I6" s="30" t="n">
+        <v>5336</v>
       </c>
       <c r="J6" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>1,316.00</t>
-        </is>
+      <c r="K6" s="30" t="n">
+        <v>1316</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -5624,10 +5623,8 @@
       <c r="H7" s="29" t="n">
         <v>-105</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>3,695.00</t>
-        </is>
+      <c r="I7" s="30" t="n">
+        <v>3695</v>
       </c>
       <c r="J7" s="29" t="n">
         <v>-10</v>
@@ -5650,42 +5647,42 @@
       <c r="C8" s="26" t="n">
         <v>13153654</v>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>20.12%</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>40.09%</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5705,42 +5702,42 @@
       <c r="C9" s="26" t="n">
         <v>13153654</v>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>2.03%</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>14.09%</t>
         </is>
       </c>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I9" s="30" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K9" s="30" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
@@ -5838,10 +5835,8 @@
       <c r="C12" s="26" t="n">
         <v>13153654</v>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>1,052.12</t>
-        </is>
+      <c r="D12" s="30" t="n">
+        <v>1052.12</v>
       </c>
       <c r="E12" s="29" t="n">
         <v>867</v>
@@ -5855,18 +5850,14 @@
       <c r="H12" s="29" t="n">
         <v>67</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>5,095.00</t>
-        </is>
+      <c r="I12" s="30" t="n">
+        <v>5095</v>
       </c>
       <c r="J12" s="29" t="n">
         <v>230</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>2,550.00</t>
-        </is>
+      <c r="K12" s="30" t="n">
+        <v>2550</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -5883,41 +5874,29 @@
       <c r="C13" s="26" t="n">
         <v>422096</v>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>4,962.40</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>2,512.00</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>7,019.66</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>5,480.00</t>
-        </is>
+      <c r="D13" s="30" t="n">
+        <v>4962.4</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>2512</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>7019.66</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>5480</v>
       </c>
       <c r="H13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>145,200.00</t>
-        </is>
+      <c r="I13" s="30" t="n">
+        <v>145200</v>
       </c>
       <c r="J13" s="29" t="n">
         <v>120</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>19,200.00</t>
-        </is>
+      <c r="K13" s="30" t="n">
+        <v>19200</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -5934,41 +5913,29 @@
       <c r="C14" s="26" t="n">
         <v>422096</v>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>4,030.05</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>1,927.00</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>5,938.42</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>4,380.00</t>
-        </is>
+      <c r="D14" s="30" t="n">
+        <v>4030.05</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>1927</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>5938.42</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>4380</v>
       </c>
       <c r="H14" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>128,500.00</t>
-        </is>
+      <c r="I14" s="30" t="n">
+        <v>128500</v>
       </c>
       <c r="J14" s="29" t="n">
         <v>85</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>15,800.00</t>
-        </is>
+      <c r="K14" s="30" t="n">
+        <v>15800</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -5985,42 +5952,42 @@
       <c r="C15" s="26" t="n">
         <v>422096</v>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>81.21%</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>83.40%</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>11.80%</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="G15" s="31" t="inlineStr">
         <is>
           <t>12.50%</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="J15" s="30" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>58.40%</t>
         </is>
       </c>
-      <c r="K15" s="30" t="inlineStr">
+      <c r="K15" s="31" t="inlineStr">
         <is>
           <t>94.20%</t>
         </is>
@@ -6040,42 +6007,42 @@
       <c r="C16" s="27" t="n">
         <v>22051557</v>
       </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>51.39%</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>50.73%</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>11.74%</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>16.20%</t>
         </is>
       </c>
-      <c r="H16" s="31" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>33.58%</t>
         </is>
       </c>
-      <c r="I16" s="31" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t>76.04%</t>
         </is>
       </c>
-      <c r="J16" s="31" t="inlineStr">
+      <c r="J16" s="32" t="inlineStr">
         <is>
           <t>35.69%</t>
         </is>
       </c>
-      <c r="K16" s="31" t="inlineStr">
+      <c r="K16" s="32" t="inlineStr">
         <is>
           <t>70.09%</t>
         </is>
@@ -6415,7 +6382,7 @@
       <c r="C6" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>37.3%</t>
         </is>
@@ -6423,7 +6390,7 @@
       <c r="E6" s="26" t="n">
         <v>1123386</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>0.605</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -6439,12 +6406,12 @@
           <t>9.85 min</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="31" t="inlineStr">
         <is>
           <t>18.00%</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr">
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t>0.89%</t>
         </is>
@@ -6464,7 +6431,7 @@
       <c r="C7" s="26" t="n">
         <v>426</v>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>31.8%</t>
         </is>
@@ -6472,7 +6439,7 @@
       <c r="E7" s="26" t="n">
         <v>1187095</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.589</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -6488,12 +6455,12 @@
           <t>15.14 min</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>23.23%</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t>1.36%</t>
         </is>
@@ -6513,7 +6480,7 @@
       <c r="C8" s="26" t="n">
         <v>224</v>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
@@ -6521,7 +6488,7 @@
       <c r="E8" s="26" t="n">
         <v>1305968</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="33" t="n">
         <v>0.576</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -6537,12 +6504,12 @@
           <t>24.17 min</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>31.04%</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t>3.16%</t>
         </is>
@@ -6562,7 +6529,7 @@
       <c r="C9" s="27" t="n">
         <v>191</v>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
@@ -6570,7 +6537,7 @@
       <c r="E9" s="27" t="n">
         <v>1215636</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="34" t="n">
         <v>0.597</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -6578,7 +6545,7 @@
           <t>55.78 min</t>
         </is>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="35" t="n">
         <v>33.07</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -6586,12 +6553,12 @@
           <t>16.51 min</t>
         </is>
       </c>
-      <c r="J9" s="31" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>24.33%</t>
         </is>
       </c>
-      <c r="K9" s="31" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t>1.82%</t>
         </is>
@@ -6727,7 +6694,7 @@
       <c r="E6" s="26" t="n">
         <v>1246150</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>0.604</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -6743,7 +6710,7 @@
           <t>15.78 min</t>
         </is>
       </c>
-      <c r="J6" s="30" t="inlineStr">
+      <c r="J6" s="31" t="inlineStr">
         <is>
           <t>23.54%</t>
         </is>
@@ -6769,7 +6736,7 @@
       <c r="E7" s="26" t="n">
         <v>1076625</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.601</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -6785,7 +6752,7 @@
           <t>11.69 min</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
         <is>
           <t>19.44%</t>
         </is>
@@ -6811,7 +6778,7 @@
       <c r="E8" s="26" t="n">
         <v>1123368</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="33" t="n">
         <v>0.594</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -6827,7 +6794,7 @@
           <t>12.22 min</t>
         </is>
       </c>
-      <c r="J8" s="30" t="inlineStr">
+      <c r="J8" s="31" t="inlineStr">
         <is>
           <t>20.05%</t>
         </is>
@@ -6853,7 +6820,7 @@
       <c r="E9" s="26" t="n">
         <v>1254744</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="33" t="n">
         <v>0.589</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -6869,7 +6836,7 @@
           <t>15.39 min</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="31" t="inlineStr">
         <is>
           <t>23.35%</t>
         </is>
@@ -6895,7 +6862,7 @@
       <c r="E10" s="26" t="n">
         <v>1241359</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="33" t="n">
         <v>0.592</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -6911,7 +6878,7 @@
           <t>16.61 min</t>
         </is>
       </c>
-      <c r="J10" s="30" t="inlineStr">
+      <c r="J10" s="31" t="inlineStr">
         <is>
           <t>24.76%</t>
         </is>
@@ -6937,7 +6904,7 @@
       <c r="E11" s="26" t="n">
         <v>1089699</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="33" t="n">
         <v>0.602</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -6953,7 +6920,7 @@
           <t>14.64 min</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J11" s="31" t="inlineStr">
         <is>
           <t>22.47%</t>
         </is>
@@ -6979,7 +6946,7 @@
       <c r="E12" s="27" t="n">
         <v>1279017</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="34" t="n">
         <v>0.577</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -6987,7 +6954,7 @@
           <t>58.07 min</t>
         </is>
       </c>
-      <c r="H12" s="34" t="n">
+      <c r="H12" s="35" t="n">
         <v>33.4</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -6995,7 +6962,7 @@
           <t>17.78 min</t>
         </is>
       </c>
-      <c r="J12" s="31" t="inlineStr">
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>25.60%</t>
         </is>
@@ -7126,10 +7093,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="36" t="n">
         <v>0.4572</v>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>20.90%</t>
         </is>
@@ -7169,10 +7136,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="36" t="n">
         <v>0.6704</v>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>44.94%</t>
         </is>
@@ -7212,10 +7179,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>0.4503</v>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>20.28%</t>
         </is>
@@ -7255,10 +7222,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="36" t="n">
         <v>0.2867</v>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>8.22%</t>
         </is>
@@ -7266,7 +7233,7 @@
       <c r="G9" s="29" t="n">
         <v>1.44</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="H9" s="33" t="n">
         <v>0.163</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -7296,10 +7263,10 @@
           <t>63,925 Airport-Days</t>
         </is>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="36" t="n">
         <v>0.4971</v>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>24.71%</t>
         </is>
@@ -7339,10 +7306,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="36" t="n">
         <v>0.2019</v>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>4.08%</t>
         </is>
@@ -7350,7 +7317,7 @@
       <c r="G11" s="29" t="n">
         <v>0.99</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="H11" s="33" t="n">
         <v>0.332</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -7380,10 +7347,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="36" t="n">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>19.14%</t>
         </is>
@@ -7423,10 +7390,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="36" t="n">
         <v>0.3714</v>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>13.79%</t>
         </is>
@@ -7434,7 +7401,7 @@
       <c r="G13" s="29" t="n">
         <v>1.92</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" s="33" t="n">
         <v>0.067</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -7464,10 +7431,10 @@
           <t>Top 25 Airfields</t>
         </is>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="36" t="n">
         <v>0.348</v>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>12.11%</t>
         </is>
@@ -7475,7 +7442,7 @@
       <c r="G14" s="29" t="n">
         <v>1.78</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="33" t="n">
         <v>0.08799999999999999</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -7505,10 +7472,10 @@
           <t>7 Days (N=7)</t>
         </is>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="36" t="n">
         <v>0.9022</v>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>81.40%</t>
         </is>
@@ -7548,10 +7515,10 @@
           <t>7 Days (N=7)</t>
         </is>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>81.00%</t>
         </is>
@@ -7591,15 +7558,15 @@
           <t>12 Months (N=12)</t>
         </is>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="37" t="n">
         <v>0.6313</v>
       </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>39.85%</t>
         </is>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="35" t="n">
         <v>2.57</v>
       </c>
       <c r="H17" s="13" t="inlineStr">

--- a/results/thesis_tables.xlsx
+++ b/results/thesis_tables.xlsx
@@ -11,21 +11,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table-format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3a" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3b" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4a" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +38,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +96,31 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -158,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +289,16 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,1648 +664,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="73" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>THESIS MASTER EMPIRICAL TABLES CATALOG (thesis_tables.xlsx)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | MSAA / Gleich 700B | Leila Gleich</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Interactive Table Index: Click any Sheet Name or Table ID to navigate directly to that table. Every worksheet includes a '⬅ Return to Table of Contents' link in Cell A1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Table ID</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Sheet Tab (Click to Jump)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Official Manuscript Table Title</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Manuscript Chapter</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Dimensions</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Scope &amp; Core Finding</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Template</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>table-format</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>APA Style Reference Template (Demographic Characteristics)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Results Appendix</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>8 rows x 4 cols</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>APA 7th Edition Sample Table Template (Clean boundary rules, no filters, no fill)</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Formatting Specification</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>MASTER THESIS RESULTS &amp; FINDINGS TABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | Gleich 700B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>Table Number</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Table Title</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>Chapter / Operational Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Table 4.1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>table_4_1</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Master Post-ETL Multi-Source Data Foundation Census (Full Candidate Commercial Network)</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>5 rows x 6 cols</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Census of 4 conformed federal feeds (TSA FOIA, BTS OTP, BTS T-100, BTS DB1B) covering 42,062,039 records</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Data Foundation &amp; ETL Census</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Master Post-ETL Multi-Source Data Foundation Census</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Data Foundation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Table 4.2</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>table_4_2</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Post-ETL Master Summary Descriptive Statistics (Top 25 Cleaned Data Warehouse)</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>11 rows x 11 cols</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Master descriptive moments (mean, std dev, median, IQR, skewness, kurtosis) across all operational variables</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Descriptive Statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.3a</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>table_4_3a</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>8 rows x 3 cols</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Comparison of Candidate A (Mature Post-Pandemic) and Candidate B (Early Post-Mask Regime; Selected, 44 months)</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Temporal Demarcation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.3b</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>table_4_3b</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 11 cols</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Annual seasonal volatility regimes (Off-Peak, Mid-Peak, Peak, Holiday) across 1,341 post-demarcation days</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Seasonality &amp; Volatility Regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Table 4.4a</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>table_4_4a</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>7 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Weekly cyclical dynamics and operational archetypes across Monday through Sunday</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Weekly Cyclical Dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Post-ETL Master Summary Descriptive Statistics</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Descriptive Scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Table 4.3</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>table_4_3</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>Master Annual Seasonal Volatility Regimes Summary</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Annual Regimes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Table 4.4</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>table_4_4</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Master Day-of-Week Operational Volatility Regimes</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (DOW Archetypes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Table 4.5</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>table_4_5</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>12 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Econometric coupling between TSA checkpoint volumes and BTS OTP delays/capacity across 12 operational dimensions</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Econometric Coupling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>Master Cross-Dataset Econometric Relationships</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Econometric Coupling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Table 4.6</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>table_4_6</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>9 rows x 7 cols</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Balanced 4x4 factorial design across 12 carrier-exclusive complexes at 9 hubs (BOS, DFW, DTW, EWR, IAH, LAX, LGA, ORD, PHL)</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Experimental Cohort Design</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Nine-Airport Experimental Cohort Factorial Specification</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (4x4 Matrix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Table 4.7</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>table_4_7</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>16 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>Formal comparison proving sample representativeness of the 9-airport experimental cohort against the Top 25 universe</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Sample Representativeness</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Cohort vs. Top 25</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Cohort Contrast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Table 4.8</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>table_4_8</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily Passenger Throughput Across the Nine Selected Airports</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>9 rows x 12 cols</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Local airport DOW profiles, weekly peak/trough days, and Peak/Trough ratios (highlighting LGA corporate profile = 2.30)</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Local Airport Demand Profiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily Passenger Throughput Across Nine Airports</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Local DOW Scale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Table 4.9</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>table_4_9</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Empirical Lead-Lag Transfer Dynamics (Scheduled Flights Versus Checkpoint Demand)</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>7 rows x 5 cols</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Asymmetric correlation and explanatory power across Lag t-1, Same-Hour t, Lead t+1, t+2, t+3, and convolved kernels</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Lead-Lag Show-Up Dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>Empirical Lead-Lag Transfer Dynamics</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Show-Up Convolution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Table 4.10</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>table_4_10</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Master Model Benchmark Matrix for TSA Throughput Volatility (2025 Full-Year Out-of-Time Holdout)</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 10 cols</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Master benchmark matrix across candidate predictive models and baseline control on 72,053 holdout observations</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Model Evaluation (Holdout)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Master Model Benchmark Matrix (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Model Accuracy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>Table 4.11</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>table_4_11</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Master Multi-Pillar Hypothesis Evaluation Matrix Across the Four Models (Throughput Volatility)</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 4: Results</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>11 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Formal empirical hypothesis test matrix across Robustness, Resilience, and Generalizability with explicit targets</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Hypothesis Testing (H1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>Master Multi-Pillar Hypothesis Evaluation Matrix</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>Chapter IV: Findings (Hypothesis 1 Test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>Table 5.1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>table_5_1</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 1: Routine Operational Accuracy Across the Candidate Models</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 8 cols</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Robustness evaluation under nominal flight conditions (RMSE, MASE, stated target MASE &lt; 0.70, Diebold-Mariano test)</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 1: Robustness</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 1: Routine Operational Accuracy (Robustness)</t>
+        </is>
+      </c>
+      <c r="D16" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Table 5.2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>table_5_2</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Resilience evaluation under severe weather ground stops and delay programs (RMSE, MASE, R_MASE ≈ 1.00, TTR &lt; 4.0h)</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 2: Resilience</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 2: Resilience Under Disruption (IROPS Regimes)</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Table 5.3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>table_5_3</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 3: Generalizability and Cross-Airport Transfer Performance</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>4 rows x 9 cols</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Zero-shot spatial transfer evaluation from EWR to LGA without retraining (RMSE, RTR = 1.00, Delta MASE &lt;= 10.0%)</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Dimension 3: Generalizability</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 3: Generalizability Across Facilities (Zero-Shot)</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Dimension 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Table 5.4</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>table_5_4</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Master Asymmetric Trade-Off Matrix Across the Candidate Models</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>3 rows x 7 cols</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Synthesis of architectural trade-offs demonstrating asymmetric performance strengths across the candidate models</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Architectural Synthesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Policy 5.1</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>Master Asymmetric Trade-Off Matrix (H1 Synthesis)</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Master Trade-Offs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>Dual-Track Policy</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>dual_track_policy</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dual-Track Operational Model Selection Policy</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 5: Discussion</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>2 rows x 6 cols</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Gated operational deployment rules for Gate 1 (Routine Flow Track -&gt; Model 2) and Gate 2 (Tactical Shock Track -&gt; Model 3)</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Deployment Policy Matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Note. Master empirical table catalog conformed across Chapter IV (Results) and Chapter V (Discussion). Formatted according to APA Style (7th ed.) with horizontal boundary rules and no filter dropdowns.</t>
-        </is>
-      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Dual-Track Operational Decision Playbook for Checkpoint Managers</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="inlineStr">
+        <is>
+          <t>Chapter V: Analysis (Operational Playbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="47" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Metric Category</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Metric</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Mean</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Std Dev</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Median</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Min (Airport)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Max (Airport)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Top 25 Mean</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Delta (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled Domestic Flights</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>224576</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>78441</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>206024</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>138,372 (PHL)</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>360,571 (ORD)</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>192160</v>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>+16.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Cancelled Flights</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>3623</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>2920</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>1,777 (DTW)</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>6,515 (DFW)</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>+32.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Flight Cancellation Rate</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>0.99% (LAX)</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2.46% (LGA)</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>+14.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Average Departure Delay</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>11.55 (DTW)</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>19.85 (DFW)</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>+7.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Significant Delay Rate (&gt;= 15m)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>21.42%</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>20.14%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>17.93% (LAX)</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>28.07% (DFW)</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>20.31%</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>+5.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Runway Taxi-Out Queue Time</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>16.96 (DTW)</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>24.67 (EWR)</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Total Passenger Throughput</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>71145628</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>27465238</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>63720916</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>40,429,531 (PHL)</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>129,069,341 (LAX)</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>68495531</v>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Average Daily Passenger Count</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>pax/day</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>53075</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>20473</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>47553</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>30,171 (PHL)</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>96,249 (LAX)</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>51138</v>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Average Hourly Passenger Count</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>418.53</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>157.02</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>239.60 (ORD)</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>662.40 (LGA)</t>
-        </is>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>540.34</v>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
-        <is>
-          <t>-22.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Peak Single-Hour Checkpoint Rush</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2673</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>881</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>2654</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>1,385 (DTW)</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>4,020 (EWR)</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>2784</v>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>-4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Demand Volatility (CV_TSA)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>0.8728</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>0.9064</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>0.6488 (BOS)</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>1.1240 (LGA)</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Passenger Share</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>47.45%</t>
-        </is>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>44.41%</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>33.58% (EWR)</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>66.32% (DFW)</t>
-        </is>
-      </c>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t>51.39%</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>-7.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Local Originating Passenger Share</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>52.55%</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>55.59%</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>33.68% (DFW)</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>66.42% (EWR)</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>48.61%</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>+8.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>True Local Originating TSA Demand</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>16376561</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>5167458</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>15995278</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>10,555,299 (DTW)</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>26,293,897 (LAX)</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>13103484</v>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>T-100 Aircraft Gauge</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Seating Capacity per Flight</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>seats</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>168.42</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>168</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>154.20 (LGA)</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>182.30 (LAX)</t>
-        </is>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>T-100 Load Factor</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Route Passenger Load Factor</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>85.08%</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>85.26%</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>83.85% (DTW)</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>86.12% (EWR)</t>
-        </is>
-      </c>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>84.73%</t>
-        </is>
-      </c>
-      <c r="J21" s="32" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2807,7 +1627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3048,7 +1868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3318,7 +2138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3923,7 +2743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4175,7 +2995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4443,7 +3263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4711,7 +3531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4914,7 +3734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6069,210 +4889,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Evaluation Criteria</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate A: Mature Post-Pandemic</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate B: Early Post-Mask Regime (Selected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>January 1, 2023</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>May 1, 2022 (RECOMMENDED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Statistical Demarcation Rationale</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Rolling Welch's t-test variance convergence</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>CUSUM structural break stabilization; Mask Mandate Repeal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Training Span</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>24 Months (2023-01 to 2024-12)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>32 Months (2022-05 to 2024-12; 20 mo train / 12 mo val)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Holdout Test Span</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>12 Months (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>12 Months (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Robustness Impact</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Excellent baseline stability; limited historical depth</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Superior: Captures two complete annual seasonal cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Resilience Impact</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Misses Winter Storm Elliott (Dec 2022)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Superior: Encapsulates severe winter freeze and summer storms</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Generalizability Impact</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Narrower training variance across spoke airfields</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Superior: 404,324 candidate multi-facility hourly records</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Coupling Rebound (R^2)</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>R^2 = 0.323 (Macro scheduled-to-TSA daily)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>R^2 rebounds from 0.368 (COVID) to 0.306–0.323 (Equilibrium)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Note. Empirical evaluation of post-pandemic temporal demarcation regimes. Candidate B (May 1, 2022 to December 31, 2025; 44 months, N = 1,341 days) was formally selected for maximum statistical power while preserving structural stability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6299,14 +4915,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.3b</t>
+          <t>Table 4.3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
+          <t>Master Annual Seasonal Volatility Regimes Summary Across the Top 25 Network</t>
         </is>
       </c>
     </row>
@@ -6579,7 +5195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6610,14 +5226,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.4a</t>
+          <t>Table 4.4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
+          <t>Master Day-of-Week Operational Volatility Regimes and Archetypes</t>
         </is>
       </c>
     </row>
@@ -6983,7 +5599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7595,7 +6211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8018,4 +6634,858 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Metric Category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Mean</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Std Dev</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Median</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Min (Airport)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Max (Airport)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Top 25 Mean</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Delta (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled Domestic Flights</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>224576</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>78441</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>206024</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>138,372 (PHL)</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>360,571 (ORD)</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>192160</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>+16.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Cancelled Flights</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>3623</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>1,777 (DTW)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>6,515 (DFW)</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>+32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Flight Cancellation Rate</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.99% (LAX)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2.46% (LGA)</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Average Departure Delay</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>11.55 (DTW)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>19.85 (DFW)</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Significant Delay Rate (&gt;= 15m)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>21.42%</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>20.14%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>17.93% (LAX)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>28.07% (DFW)</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>20.31%</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Runway Taxi-Out Queue Time</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>16.96 (DTW)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>24.67 (EWR)</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Total Passenger Throughput</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>71145628</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>27465238</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>63720916</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>40,429,531 (PHL)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>129,069,341 (LAX)</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>68495531</v>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Average Daily Passenger Count</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>pax/day</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>53075</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>20473</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>47553</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>30,171 (PHL)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>96,249 (LAX)</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>51138</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Average Hourly Passenger Count</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>418.53</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>157.02</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>239.60 (ORD)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>662.40 (LGA)</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>540.34</v>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>-22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Peak Single-Hour Checkpoint Rush</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2673</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>881</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1,385 (DTW)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>4,020 (EWR)</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>2784</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Demand Volatility (CV_TSA)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>0.6488 (BOS)</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>1.1240 (LGA)</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Connecting Passenger Share</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>47.45%</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>44.41%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>33.58% (EWR)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>66.32% (DFW)</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>51.39%</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>-7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Local Originating Passenger Share</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>52.55%</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>55.59%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>33.68% (DFW)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>66.42% (EWR)</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>48.61%</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>True Local Originating TSA Demand</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>16376561</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>5167458</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>15995278</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>10,555,299 (DTW)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>26,293,897 (LAX)</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>13103484</v>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T-100 Aircraft Gauge</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Seating Capacity per Flight</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>seats</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>168</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>154.20 (LGA)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>182.30 (LAX)</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>T-100 Load Factor</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Route Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>85.26%</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>83.85% (DTW)</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>86.12% (EWR)</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>84.73%</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/thesis_tables.xlsx
+++ b/results/thesis_tables.xlsx
@@ -11,20 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table-format" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3a" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_3b" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_4a" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_5" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_6" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_7" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_8" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_9" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_10" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_4_11" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_5_4" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dual_track_policy" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,31 +97,6 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -182,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -289,16 +265,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -664,434 +630,1648 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="92" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="73" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="40" t="inlineStr">
-        <is>
-          <t>MASTER THESIS RESULTS &amp; FINDINGS TABLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="41" t="inlineStr">
-        <is>
-          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | Gleich 700B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>Table Number</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>Sheet Name</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Table Title</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Chapter / Operational Scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>THESIS MASTER EMPIRICAL TABLES CATALOG (thesis_tables.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Evaluating Predictive Techniques to Model Stochastic Airport Passenger Flow | MSAA / Gleich 700B | Leila Gleich</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Interactive Table Index: Click any Sheet Name or Table ID to navigate directly to that table. Every worksheet includes a '⬅ Return to Table of Contents' link in Cell A1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Table ID</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sheet Tab (Click to Jump)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Official Manuscript Table Title</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Manuscript Chapter</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Scope &amp; Core Finding</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>table-format</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>APA Style Reference Template (Demographic Characteristics)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Results Appendix</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>8 rows x 4 cols</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>APA 7th Edition Sample Table Template (Clean boundary rules, no filters, no fill)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Formatting Specification</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Table 4.1</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>table_4_1</t>
         </is>
       </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>Master Post-ETL Multi-Source Data Foundation Census</t>
-        </is>
-      </c>
-      <c r="D5" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Data Foundation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Master Post-ETL Multi-Source Data Foundation Census (Full Candidate Commercial Network)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>5 rows x 6 cols</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Census of 4 conformed federal feeds (TSA FOIA, BTS OTP, BTS T-100, BTS DB1B) covering 42,062,039 records</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Data Foundation &amp; ETL Census</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Table 4.2</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>table_4_2</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>Post-ETL Master Summary Descriptive Statistics</t>
-        </is>
-      </c>
-      <c r="D6" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Descriptive Scale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Table 4.3</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>table_4_3</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
-        <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Annual Regimes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>Table 4.4</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>table_4_4</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>Master Day-of-Week Operational Volatility Regimes</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (DOW Archetypes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Post-ETL Master Summary Descriptive Statistics (Top 25 Cleaned Data Warehouse)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>11 rows x 11 cols</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Master descriptive moments (mean, std dev, median, IQR, skewness, kurtosis) across all operational variables</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Descriptive Statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.3a</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>table_4_3a</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>8 rows x 3 cols</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Comparison of Candidate A (Mature Post-Pandemic) and Candidate B (Early Post-Mask Regime; Selected, 44 months)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Temporal Demarcation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.3b</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>table_4_3b</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 11 cols</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Annual seasonal volatility regimes (Off-Peak, Mid-Peak, Peak, Holiday) across 1,341 post-demarcation days</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Seasonality &amp; Volatility Regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Table 4.4a</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>table_4_4a</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>7 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Weekly cyclical dynamics and operational archetypes across Monday through Sunday</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Weekly Cyclical Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Table 4.5</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>table_4_5</t>
         </is>
       </c>
-      <c r="C9" s="45" t="inlineStr">
-        <is>
-          <t>Master Cross-Dataset Econometric Relationships</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Econometric Coupling)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Master Cross-Dataset Econometric Relationships (Top 25 Airfields)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>12 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Econometric coupling between TSA checkpoint volumes and BTS OTP delays/capacity across 12 operational dimensions</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Econometric Coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Table 4.6</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>table_4_6</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Nine-Airport Experimental Cohort Factorial Specification</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (4x4 Matrix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>The Nine-Airport Experimental Cohort Factorial Specification</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>9 rows x 7 cols</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Balanced 4x4 factorial design across 12 carrier-exclusive complexes at 9 hubs (BOS, DFW, DTW, EWR, IAH, LAX, LGA, ORD, PHL)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Experimental Cohort Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Table 4.7</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>table_4_7</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Cohort vs. Top 25</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Cohort Contrast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>16 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Formal comparison proving sample representativeness of the 9-airport experimental cohort against the Top 25 universe</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Sample Representativeness</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Table 4.8</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>table_4_8</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>Day-of-Week Mean Daily Passenger Throughput Across Nine Airports</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Local DOW Scale)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Day-of-Week Mean Daily Passenger Throughput Across the Nine Selected Airports</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>9 rows x 12 cols</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Local airport DOW profiles, weekly peak/trough days, and Peak/Trough ratios (highlighting LGA corporate profile = 2.30)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Local Airport Demand Profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Table 4.9</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>table_4_9</t>
         </is>
       </c>
-      <c r="C13" s="45" t="inlineStr">
-        <is>
-          <t>Empirical Lead-Lag Transfer Dynamics</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Show-Up Convolution)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Empirical Lead-Lag Transfer Dynamics (Scheduled Flights Versus Checkpoint Demand)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>7 rows x 5 cols</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Asymmetric correlation and explanatory power across Lag t-1, Same-Hour t, Lead t+1, t+2, t+3, and convolved kernels</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Lead-Lag Show-Up Dynamics</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Table 4.10</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>table_4_10</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t>Master Model Benchmark Matrix (2025 Full-Year Holdout)</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Model Accuracy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Master Model Benchmark Matrix for TSA Throughput Volatility (2025 Full-Year Out-of-Time Holdout)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 10 cols</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Master benchmark matrix across candidate predictive models and baseline control on 72,053 holdout observations</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Model Evaluation (Holdout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Table 4.11</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>table_4_11</t>
         </is>
       </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>Master Multi-Pillar Hypothesis Evaluation Matrix</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="inlineStr">
-        <is>
-          <t>Chapter IV: Findings (Hypothesis 1 Test)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Master Multi-Pillar Hypothesis Evaluation Matrix Across the Four Models (Throughput Volatility)</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 4: Results</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>11 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Formal empirical hypothesis test matrix across Robustness, Resilience, and Generalizability with explicit targets</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Hypothesis Testing (H1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Table 5.1</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>table_5_1</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 1: Routine Operational Accuracy (Robustness)</t>
-        </is>
-      </c>
-      <c r="D16" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 1: Routine Operational Accuracy Across the Candidate Models</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 8 cols</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Robustness evaluation under nominal flight conditions (RMSE, MASE, stated target MASE &lt; 0.70, Diebold-Mariano test)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 1: Robustness</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Table 5.2</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>table_5_2</t>
         </is>
       </c>
-      <c r="C17" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 2: Resilience Under Disruption (IROPS Regimes)</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 2: Resilience and Shock Performance Under Severe Operational Disruption</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Resilience evaluation under severe weather ground stops and delay programs (RMSE, MASE, R_MASE ≈ 1.00, TTR &lt; 4.0h)</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 2: Resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Table 5.3</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>table_5_3</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
-        <is>
-          <t>Evaluation Dimension 3: Generalizability Across Facilities (Zero-Shot)</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Dimension 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation Dimension 3: Generalizability and Cross-Airport Transfer Performance</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>4 rows x 9 cols</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Zero-shot spatial transfer evaluation from EWR to LGA without retraining (RMSE, RTR = 1.00, Delta MASE &lt;= 10.0%)</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Dimension 3: Generalizability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Table 5.4</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>table_5_4</t>
         </is>
       </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>Master Asymmetric Trade-Off Matrix (H1 Synthesis)</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Master Trade-Offs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>Dual-Track Policy</t>
-        </is>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Master Asymmetric Trade-Off Matrix Across the Candidate Models</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>3 rows x 7 cols</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Synthesis of architectural trade-offs demonstrating asymmetric performance strengths across the candidate models</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Architectural Synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Policy 5.1</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>dual_track_policy</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>Dual-Track Operational Decision Playbook for Checkpoint Managers</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
-        <is>
-          <t>Chapter V: Analysis (Operational Playbook)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="47" t="n"/>
-      <c r="B21" s="47" t="n"/>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Dual-Track Operational Model Selection Policy</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Chapter 5: Discussion</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>2 rows x 6 cols</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Gated operational deployment rules for Gate 1 (Routine Flow Track -&gt; Model 2) and Gate 2 (Tactical Shock Track -&gt; Model 3)</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Deployment Policy Matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Note. Master empirical table catalog conformed across Chapter IV (Results) and Chapter V (Discussion). Formatted according to APA Style (7th ed.) with horizontal boundary rules and no filter dropdowns.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Metric Category</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Operational Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Mean</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Std Dev</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Median</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Min (Airport)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>9-Airport Max (Airport)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Top 25 Mean</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Delta (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Scheduled Domestic Flights</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>224576</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>78441</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>206024</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>138,372 (PHL)</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>360,571 (ORD)</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>192160</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>+16.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Cancelled Flights</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>3623</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>1,777 (DTW)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>6,515 (DFW)</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>2738</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>+32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Flight Cancellation Rate</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.99% (LAX)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2.46% (LGA)</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>+14.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Average Departure Delay</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>11.55 (DTW)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>19.85 (DFW)</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Significant Delay Rate (&gt;= 15m)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>21.42%</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>20.14%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>17.93% (LAX)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>28.07% (DFW)</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>20.31%</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>BTS OTP Delays</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Runway Taxi-Out Queue Time</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>16.96 (DTW)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>24.67 (EWR)</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Total Passenger Throughput</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>71145628</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>27465238</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>63720916</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>40,429,531 (PHL)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>129,069,341 (LAX)</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>68495531</v>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Average Daily Passenger Count</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>pax/day</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>53075</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>20473</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>47553</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>30,171 (PHL)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>96,249 (LAX)</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>51138</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Average Hourly Passenger Count</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>418.53</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>157.02</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>239.60 (ORD)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>662.40 (LGA)</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>540.34</v>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>-22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Peak Single-Hour Checkpoint Rush</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>pax/hr</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2673</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>881</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>2654</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1,385 (DTW)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>4,020 (EWR)</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>2784</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TSA Checkpoint</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Demand Volatility (CV_TSA)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>0.6488 (BOS)</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>1.1240 (LGA)</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Connecting Passenger Share</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>47.45%</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>44.41%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>33.58% (EWR)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>66.32% (DFW)</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>51.39%</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>-7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Local Originating Passenger Share</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>52.55%</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>10.98%</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>55.59%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>33.68% (DFW)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>66.42% (EWR)</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr">
+        <is>
+          <t>48.61%</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>+8.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>BTS DB1B Surveys</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>True Local Originating TSA Demand</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>pax</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>16376561</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>5167458</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>15995278</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>10,555,299 (DTW)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>26,293,897 (LAX)</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>13103484</v>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T-100 Aircraft Gauge</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Seating Capacity per Flight</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>seats</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>168.42</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>168</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>154.20 (LGA)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>182.30 (LAX)</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>T-100 Load Factor</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Route Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>85.08%</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>85.26%</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>83.85% (DTW)</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>86.12% (EWR)</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>84.73%</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1627,7 +2807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1868,7 +3048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2138,7 +3318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2743,7 +3923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2995,7 +4175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3263,7 +4443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3531,7 +4711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3734,7 +4914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4889,6 +6069,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⬅ Return to Table of Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Table 4.3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Post-Pandemic Temporal Demarcation Evaluation Across the Top 25 Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Evaluation Criteria</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Candidate A: Mature Post-Pandemic</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Candidate B: Early Post-Mask Regime (Selected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>January 1, 2023</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>May 1, 2022 (RECOMMENDED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Statistical Demarcation Rationale</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Rolling Welch's t-test variance convergence</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>CUSUM structural break stabilization; Mask Mandate Repeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Training Span</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>24 Months (2023-01 to 2024-12)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>32 Months (2022-05 to 2024-12; 20 mo train / 12 mo val)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Holdout Test Span</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>12 Months (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>12 Months (2025 Full-Year Holdout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Robustness Impact</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Excellent baseline stability; limited historical depth</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Superior: Captures two complete annual seasonal cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Resilience Impact</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Misses Winter Storm Elliott (Dec 2022)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Superior: Encapsulates severe winter freeze and summer storms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Generalizability Impact</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Narrower training variance across spoke airfields</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Superior: 404,324 candidate multi-facility hourly records</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Coupling Rebound (R^2)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>R^2 = 0.323 (Macro scheduled-to-TSA daily)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>R^2 rebounds from 0.368 (COVID) to 0.306–0.323 (Equilibrium)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Note. Empirical evaluation of post-pandemic temporal demarcation regimes. Candidate B (May 1, 2022 to December 31, 2025; 44 months, N = 1,341 days) was formally selected for maximum statistical power while preserving structural stability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4915,14 +6299,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.3</t>
+          <t>Table 4.3b</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Annual Seasonal Volatility Regimes Summary Across the Top 25 Network</t>
+          <t>Master Annual Seasonal Volatility Regimes Summary (Top 25 Airfields)</t>
         </is>
       </c>
     </row>
@@ -5195,7 +6579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5226,14 +6610,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Table 4.4</t>
+          <t>Table 4.4a</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>Master Day-of-Week Operational Volatility Regimes and Archetypes</t>
+          <t>Day-of-Week Volatility Dynamics and Operational Archetypes (Top 25 Airfields)</t>
         </is>
       </c>
     </row>
@@ -5599,7 +6983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5611,7 +6995,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -5876,7 +7260,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>63,925 Airport-Days</t>
+          <t>Top 25 Airfields</t>
         </is>
       </c>
       <c r="E10" s="36" t="n">
@@ -6211,7 +7595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6634,858 +8018,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Table 4.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Summary Descriptive Statistics: Nine-Airport Experimental Cohort Versus Top 25 Universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Metric Category</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Operational Metric</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Mean</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Std Dev</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Median</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Min (Airport)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>9-Airport Max (Airport)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Top 25 Mean</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Delta (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Scheduled Domestic Flights</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>224576</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>78441</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>206024</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>138,372 (PHL)</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>360,571 (ORD)</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>192160</v>
-      </c>
-      <c r="J6" s="31" t="inlineStr">
-        <is>
-          <t>+16.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Cancelled Flights</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>3623</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>2920</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>1,777 (DTW)</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>6,515 (DFW)</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>2738</v>
-      </c>
-      <c r="J7" s="31" t="inlineStr">
-        <is>
-          <t>+32.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Operations</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Flight Cancellation Rate</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>0.99% (LAX)</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2.46% (LGA)</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="J8" s="31" t="inlineStr">
-        <is>
-          <t>+14.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Average Departure Delay</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>11.55 (DTW)</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>19.85 (DFW)</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>+7.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Significant Delay Rate (&gt;= 15m)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>21.42%</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>20.14%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>17.93% (LAX)</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>28.07% (DFW)</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t>20.31%</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>+5.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>BTS OTP Delays</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Runway Taxi-Out Queue Time</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>20.59</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>16.96 (DTW)</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>24.67 (EWR)</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Total Passenger Throughput</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>71145628</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>27465238</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>63720916</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>40,429,531 (PHL)</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>129,069,341 (LAX)</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>68495531</v>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Average Daily Passenger Count</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>pax/day</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>53075</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>20473</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>47553</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>30,171 (PHL)</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>96,249 (LAX)</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>51138</v>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>+3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Average Hourly Passenger Count</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>418.53</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>157.02</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>239.60 (ORD)</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>662.40 (LGA)</t>
-        </is>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>540.34</v>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
-        <is>
-          <t>-22.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Peak Single-Hour Checkpoint Rush</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>pax/hr</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2673</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>881</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>2654</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>1,385 (DTW)</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>4,020 (EWR)</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>2784</v>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>-4.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TSA Checkpoint</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Demand Volatility (CV_TSA)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>0.8728</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>0.9064</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>0.6488 (BOS)</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>1.1240 (LGA)</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>+5.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Connecting Passenger Share</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>47.45%</t>
-        </is>
-      </c>
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>44.41%</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>33.58% (EWR)</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>66.32% (DFW)</t>
-        </is>
-      </c>
-      <c r="I17" s="31" t="inlineStr">
-        <is>
-          <t>51.39%</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>-7.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Local Originating Passenger Share</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>52.55%</t>
-        </is>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>10.98%</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>55.59%</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>33.68% (DFW)</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>66.42% (EWR)</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="inlineStr">
-        <is>
-          <t>48.61%</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>+8.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>BTS DB1B Surveys</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>True Local Originating TSA Demand</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>pax</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>16376561</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>5167458</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>15995278</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>10,555,299 (DTW)</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>26,293,897 (LAX)</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>13103484</v>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>T-100 Aircraft Gauge</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Seating Capacity per Flight</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>seats</t>
-        </is>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>168.42</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>168</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>154.20 (LGA)</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>182.30 (LAX)</t>
-        </is>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>T-100 Load Factor</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Route Passenger Load Factor</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>85.08%</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>85.26%</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>83.85% (DTW)</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>86.12% (EWR)</t>
-        </is>
-      </c>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>84.73%</t>
-        </is>
-      </c>
-      <c r="J21" s="32" t="inlineStr">
-        <is>
-          <t>+0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Note. Formal Welch's two-sample t-tests demonstrating no statistically significant differences between the 9-airport experimental cohort and the Top 25 airport universe across operational metrics (all p &gt; 0.05).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>